--- a/src/reporteria/plantillas/Empresas_Reporteria.xlsx
+++ b/src/reporteria/plantillas/Empresas_Reporteria.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="34">
   <si>
     <t>EmpresaId</t>
   </si>
@@ -64,6 +64,12 @@
   </si>
   <si>
     <t>Localidad</t>
+  </si>
+  <si>
+    <t>Vía Origen</t>
+  </si>
+  <si>
+    <t>Vía Destino</t>
   </si>
   <si>
     <t>Total Movimientos</t>
@@ -499,7 +505,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q1"/>
+  <dimension ref="A1:S1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -510,10 +516,10 @@
     <col min="11" max="11" width="16" customWidth="1"/>
     <col min="12" max="13" width="10" customWidth="1"/>
     <col min="14" max="16" width="24" customWidth="1"/>
-    <col min="17" max="17" width="20" customWidth="1"/>
+    <col min="17" max="19" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -564,6 +570,12 @@
       </c>
       <c r="Q1" s="1" t="s">
         <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -593,31 +605,31 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -633,32 +645,32 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B8" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
